--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -593,6 +593,13 @@
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>CN-33 与 DD-41 记录 AS-14 的推翻：四角色不变，但调度员与主管按派驻部门切分数据。DD-19 的预留在此兑现，故本次为启用而非重构。DD-40 同轮新增。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>DD-43 至 DD-48 与 CN-34 为组件选型讨论新增。其中 DD-46 修正了 DD-15 弃用 MinIO 的理由——原以 AGPL 为据不成立，真正的理由是上游已归档停止维护；该条同时确立「上游健康度优先于许可」的选型标准。按维护规则，DD-15 保留原文不改。</t>
         </is>
       </c>
     </row>
@@ -607,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1706,6 +1713,38 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>CN-34</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>技术栈横跨 Python、Java 与 Node 三个运行时</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>技术固有</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>技术固有</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Superset、Airflow、dbt 与报表渲染为 Python，Keycloak 为 Java，前端与移动薄壳为 Node。在无互联网环境（CN-12）下意味着须维护三套内网镜像源（PyPI、Maven、npm），外加容器镜像仓库与操作系统包源，共五条离线供给链。这是 LD-08 与 LD-09 必须覆盖的实际工作量，也是 REQ-LIC-08「合同期内保持最新稳定版本」的落地成本。唯一有意义的削减候选是 Keycloak，但自实现 OIDC 联邦得不偿失，不予考虑。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>REQ-SEC-06 · REQ-LIC-08 · DD-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1718,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3537,6 +3576,258 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>DD-43</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>监控可视化改为自建，不引入 Grafana</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>M-08 运行监控需要可用性、复制延迟、查询时延分布与资源水位的可视化。通行做法是 Prometheus 加 Grafana。</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Prometheus（Apache 2.0）负责采集与告警评估；可视化建在本方门户中，作为 M-08 的一部分交付。</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>引入 Grafana 作为监控可视化。</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Grafana 自 8.0 起为 AGPLv3。本项目已因 AGPL 弃用过 MinIO（DD-15），若在监控上引入 AGPL 组件将出现口径不一致，评标与 MOI 合规审查都会追问。改为自建的额外工作量很小——四十张报表本就要建图表组件库——且与 RFP 1.6.2.19 要求的单一集成报表方案一致：监控视图与业务报表同一门户、同一权限模型。</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>低（可视化层，采集与告警不受影响）</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>REQ-OPS-02 · REQ-AVL-04 · DD-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>DD-44</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>保留 Airflow 作为批量编排器</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>M-02 要求运行历史、依赖视图、失败重跑、补数与 SLA 告警。DD-11 曾以「27 台虚机、数十用户的规模下自身复杂度超过所解决的问题」为由拒绝 Kubernetes，同一把尺子需对 Airflow 量一次。</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>采用 Airflow（Apache 2.0）。DAG 由接入契约注册表动态生成（HLD 4.1），元数据库复用 PostgreSQL 集群但置于独立数据库，不与业务库混用。</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>以 cron 加 dbt 加自建运行状态表替代，把 M-02 建在 meta.run_log 之上。</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>两者规模判断的结论不同：Kubernetes 解决的是本项目并不存在的问题（弹性调度、服务编排），而 Airflow 解决的是每天都要用的问题——失败重跑与补数。自建这两项容易做成半成品，而它们恰是运维日常最依赖的功能。代价是多一套 Python 依赖链需纳入离线镜像（CN-34）。</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>中（编排器更换须重写 DAG 生成逻辑，但契约与模型不受影响）</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · REQ-OPS-02 · DD-05 · DD-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>DD-45</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>服务水平举证数据落 audit schema，不新增第八个 schema</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>监控数据须独立留存、只增不改、保留期与考核期一致（HLD 9.3 · 11.6），而考核按日、合同期八年。Prometheus 默认不做长期存储。</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>分两层：Prometheus 保存短期运行态（数周，供排障）；按日聚合的服务水平证据落 audit schema 的专用表，八年只增不改，与访问留痕同域管理。</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>一、引入 Thanos 或 VictoriaMetrics 做时序长期存储。二、为服务水平证据新增独立 schema。</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>一、服务水平证据基数极低（每日每组件数行），用时序库的长期存储方案属杀鸡用牛刀，且多一个组件要纳入离线补丁链。二、REQ-MOD-01 的验收标准是「库中存在且仅存在这七个业务 schema」，新增第八个会与之冲突；audit 的只增不改语义与举证数据的要求天然一致，是正确的归属。</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>低（存储位置，不影响采集与判定口径）</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>REQ-AVL-04 · REQ-OPS-02 · REQ-MOD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>DD-46</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>组件上游健康度列为一等选型标准，排在许可之前；DD-15 的理由随之修正</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>DD-15 以 AGPL 为由弃用 MinIO。经复核，该理由不成立：AGPLv3 相对 GPLv3 多出的第 13 条以「修改」为触发条件，我方不修改 MinIO 而仅将其作为网络服务使用，故与 PostGIS 的 GPLv2 属同一性质；若以许可为由弃用 MinIO，则同样应弃用 PostGIS，而我们并未如此。真正决定性的事实是另一件：MinIO 社区版于 2025 年 12 月进入维护模式、2026 年 4 月 25 日仓库归档转为只读，最后一次官方安全更新为 2025 年 10 月。</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>弃用 MinIO 的结论不变，理由改为「上游已终止维护」。同时确立选型标准：组件的上游健康度（治理模式、发布节奏、安全响应记录、社区规模）优先于许可类型；且不是选型时评估一次，而是作为组件清单中的常设字段定期复核（LD-09）。按此标准复核现有组件，PostgreSQL、PostGIS、Airflow、Superset、etcd、Keycloak、Prometheus、Podman、Ansible、HAProxy、React 属基金会或社区治理，风险低；SeaweedFS、Patroni、WeasyPrint、dbt-core 属单一公司或单一维护者主导，需持续关注。dbt-core 经核为 Apache 2.0 且承诺无限期维护，2025 年的 ELv2 代码已于 2026 年 6 月重新以 Apache 2.0 授权并并入 dbt-core，该项风险目前解除。</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>一、维持以许可作为首要排除标准。二、仅在选型时评估一次上游状况。</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>一、以许可为首要标准会同时误伤 PostGIS、HAProxy 与 Ansible，且会漏掉 MinIO 这类真正的风险——它的问题与许可无关。二、AS-01 的整套 COTS 五年论证建立在「核心开源组件公开发布满五年且上游活跃」之上；上游状态会变化，一次性评估无法支撑八年合同期的举证。</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>高（选型方法论，影响全部组件）</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>REQ-LIC-02 · REQ-LIC-07 · REQ-LIC-08 · AS-01 · CN-09 · DD-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>DD-47</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>对象存储维持 SeaweedFS，并定死重新评估的触发条件</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MinIO 出局后需确认对象存储选择。候选为 SeaweedFS（Apache 2.0，活跃但以单一维护者为主）、Garage（AGPLv3，活跃，集体治理）与 Ceph RGW（LGPL/GPL，成熟，基金会治理，多站复制方案成熟）。未来七中心联网与 VMS 加 AI 告警带来的媒体量增长均为可能而非既定。</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>本期维持 SeaweedFS。同时明确两点：一、架构上已有缓冲——对象存储只经媒体服务访问，客户端从不直接接触（HLD 3.2.4 · 7.5），更换实现是被服务层包住的局部改动；这条原本是安全设计，现在同时是供应风险的缓冲。二、重新评估的触发条件为下列任一：七中心联网确定立项、媒体量超过 50 TB、或 SeaweedFS 上游出现维护中断迹象。另在实施前期安排一次对比验证（SeaweedFS、Garage、Ceph RGW 最小可行部署），产出的选型报告同时作为 CN-09 五年论证的举证材料；虚机资源单按 Ceph 规格预留余量，避免事后追加成为变更请求。</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>一、本期即改用 Ceph RGW。二、改用 Garage。三、不设触发条件，届时再议。</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>一、三节点、10 至 50 TB 的场景下 Ceph 的守护进程种类、OSD 内存开销与恢复再平衡的延迟尖峰，其运维分量超过所解决的问题——与 DD-11 拒绝 Kubernetes 同一推理；且七中心联网并不自动要求存储层复制，跨站媒体访问可由媒体服务按站点路由解决，那样更符合服务层唯一出口，也避免让各站点在存储层耦合故障域。二、Garage 在许可上现已合格，但成熟度与 S3 特性覆盖不及 SeaweedFS，换过去收益不明确。三、不设触发条件则重新评估永远不会发生，MinIO 的教训正在于此。</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>中（受服务层封装保护，更换为局部改动）</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>REQ-MOD-07 · REQ-BAK-04 · DD-15 · DD-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>DD-48</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>DD-31 的「列存加速层」泛化为「派生查询引擎」，并补入全文检索触发条件</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>VMS 加 AI 智能告警若成为业务方向，事件行数可能达到当前警情量的一到两个数量级；七中心联网会再乘以七。同时语音转写与警情描述可能产生阿拉伯语全文检索需求。DD-31 原只为列存引擎预设了形态与触发条件。</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>把 DD-31 的适用范围由列存引擎泛化为一切派生查询引擎，形态约束不变：只能作为只读投影，数据由 core 与 mart 单向灌入，永不作为记录系统。触发条件新增一条——需要对警情描述、处置反馈或语音转写做阿拉伯语全文检索。若届时启用检索引擎，选 OpenSearch（Apache 2.0，Linux 基金会治理）而非 Elasticsearch。四项今日即做的低成本准备：保持 kafka_consume 契约预留（DD-10）；全文字段在 core 中具备稳定实体主键与时间语义，使检索引擎的文档 id 可直接采用 core.sk 的值、重建幂等而无须映射表；不在 PostgreSQL 中搭建将来要废弃的全文检索设施；投影链路一律建在 L3，不得让 L4 之外的任何层直接访问检索引擎。</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>一、以行数作为触发条件。二、若启用则选 Elasticsearch。三、现在即在 PostgreSQL 中建设阿拉伯语全文检索。</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>一、PostgreSQL 在亿行量级仍可依靠分区与索引支撑，真正的卡点是阿拉伯语全文检索——内置全文检索缺少阿语词干与词形还原。按行数写触发条件会在错误的时点触发。二、Elastic 五年内两度变更许可（2021 转 SSPL/ELv2，2024 增加 AGPLv3 选项），在需要论证未来五年不 EOL 的方案中，基金会治理的 OpenSearch 明显更易举证（DD-46）。三、当前范围（结构化条件的记录检索）不需要全文；若仅需描述字段的模糊匹配，pg_trgm 加 GIN 在千万行量级已足够，且属过渡手段而非投资。</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>高（架构级预设，决定将来迁移的成本落在哪几层）</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>REQ-MOD-07 · REQ-PRF-01 · DD-02 · DD-03 · DD-10 · DD-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -600,6 +600,34 @@
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>DD-43 至 DD-48 与 CN-34 为组件选型讨论新增。其中 DD-46 修正了 DD-15 弃用 MinIO 的理由——原以 AGPL 为据不成立，真正的理由是上游已归档停止维护；该条同时确立「上游健康度优先于许可」的选型标准。按维护规则，DD-15 保留原文不改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CN-35 与 DD-49 补上了一处漏项：HLD 9.2 以「Git 为权威」为前提，但组件清单与虚机资源表中从无代码仓库。结论是生产网内不部署，改由发布制品、对象存储中的历史版本与 meta.release_registry 承担。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DD-50 补正 DD-35 的缓存键定义——原规定只挡住列的串号，挡不住行的。DD-51 改变了受控 SQL 的授权方式：由按角色改为按自然人显式授权，系统一律经服务层不另开通道。按维护规则 DD-35 与 DD-18 保留原文不改；DD-51 在同一轮讨论中定稿，系统主体一案记入其被拒绝的方案列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CN-36 与 DD-52 更正了归档库的数据库产品：为 SQL Server 而非此前记录的 PostgreSQL。这是一条已确认客户答复被推翻的实例，连带影响接入连接器、接口协议、类型映射、插图与组件清单。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【2026-09 补充】DD-53 至 DD-55 为详细设计第二轮讨论结论：旁路数据源经逐项核实后清空——排班改派生、勤务级别保留非必选接口、质检属 IRMS 不在范围。本系统因此不存在人工录入的业务数据源，M-10 仅维护参照数据。</t>
         </is>
       </c>
     </row>
@@ -614,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1745,6 +1773,70 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>CN-35</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>MOI 生产网内无既有的制品仓库或配置管理平台，且不在项目范围内</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>现场条件 + 商务范围</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>现场条件</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>结构性配置的版本管理须由本方在发布制品与 meta 登记表中自足实现，导入流程不依赖任何外部平台，制品的完整性校验由本方负责。同时开发不在 MOI 现场进行，生产网气隙隔离且不与外网同步——生产网内的代码仓库将是无人提交的孤岛。见 DD-49。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>REQ-OPS-04 · REQ-LIC-07 · DD-05 · DD-49</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>CN-36</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>归档库为 SQL Server（Hexagon 原生），读取 archive 副本库</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>现场条件</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>现场条件</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>推翻此前记录的「归档库为 PostgreSQL」（HD-03 客户答复表，系早期沟通误记）。后果有四：一、接入需新增第五类连接器 mssql_read，契约的 connector 枚举与 meta.source_contract 的 CHECK 约束随之扩展；二、IF-01 的协议由 PostgreSQL wire 改为 TDS，图 3-1 与 3-2 须重画；三、跨库类型映射成为 LD-01 的实质内容，其中时间类型最要紧——SQL Server 的 datetime 与 datetime2 不带时区，若源端未用 datetimeoffset，则 REQ-MIG-08「保留原始时区」在源头即不成立，须在迁移方案中如实表述（IR-42）；四、驱动链须为开源，见 DD-52。读取 archive 副本库而非生产库，正好满足 REQ-MIG-05 迁移对现有环境零影响。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>REQ-MIG-01 · REQ-MIG-05 · REQ-MIG-08 · REQ-ING-01 · AS-02 · IR-42 · DD-52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1757,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3828,6 +3920,510 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>DD-49</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>结构性配置的版本管理：发布制品加登记表，生产网内不部署代码仓库</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>HLD 9.2 规定结构性配置以 Git 为权威、库内副本只读，但组件清单与 12.1 的虚机资源表中均无代码仓库服务——这是一处漏项。厘清后的事实是：开发不在 MOI 现场进行；生产网气隙隔离且不允许与外网同步；MOI 生产网内亦无可对接的制品仓库或配置管理平台（CN-35）。生产侧仍须能回答三个问题：现在跑的是哪一版契约、模型与指标定义；上个月出报表时用的是哪一版；出问题如何回到上一版。</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>开发侧 Git 为唯一权威，生产网内既不部署代码仓库，也不自研独立的版本管理工具。生产侧的版本管理由三部分承担。一、发布制品：接入契约、dbt 模型、指标定义、DDL、部署脚本与组件清单打包为带版本号与 SHA-256 校验和的不可变制品，manifest 中携带变更摘要与评审记录——评审发生在开发侧，但证据必须随制品进入生产，否则运维侧只看得到版本号变了、看不到为什么。二、制品存入对象存储的独立前缀，每次变更留一版，历史版本原则上不删除，可追溯可回滚；保留策略在 meta.retention_policy 中单列，不适用 DD-38 的三层期限。三、meta.release_registry 登记每次发布；M-01 与 M-04 增加只读的版本区块，展示当前版本、历史版本与每版变更。回滚即从对象存储取回上一制品重新导入，不依赖联网。</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>一、在 MOI 生产网内部署 Forgejo 或其它代码仓库服务。二、自研独立的版本管理工具。三、制品仅存于本地文件系统。</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>一、生产网与开发侧气隙隔离，该仓库无人提交，只会增加一条离线补丁链、一个备份对象与一处攻击面，不解决任何实际问题。二、自研工具须实现版本、校验、留痕与回滚四项，做完并不简单；更关键的是它成为本方需维护八年的对象，会进入 CN-09 的五年举证清单——采用他方维护的组件时该负担不在我方，自研则相反。三、本地文件系统无法满足历史不删除与可追溯的要求，也不在备份与容量管理的统一口径内。</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>中（生产侧机制为登记表与导入流程；开发侧权威不受影响）</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>REQ-OPS-04 · REQ-LIC-07 · REQ-BAK-04 · DD-05 · CN-12 · CN-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>DD-50</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>查询缓存的键必须包含完整权限上下文，补正 DD-35</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>DD-35 规定缓存键须包含字段白名单指纹。该规定只挡住了列的串号，挡不住行的：民防的调度员与警察的调度员角色相同、字段白名单完全相同，但可见行不同（DD-41）。若缓存键不含部门，第二人的查询将命中第一人的缓存，直接看到对方警种的数据——不报错，静默泄露，与 DD-35 当初要防的是同一类问题。</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>缓存键由完整的权限上下文哈希构成，至少包含角色、部门、字段白名单指纹与查询指纹四项。实现上取权限上下文对象整体哈希，而非逐项拼接——这样将来权限模型再增维度（如按辖区、按时间范围授权）不会重演本次遗漏。缓存条目在权限变更时按主体失效。</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>一、仅按 DD-35 的字段白名单指纹分键。二、对涉及行过滤的查询一律禁用缓存。</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>一、见背景，会造成跨部门的行级串号。二、行过滤覆盖绝大多数业务查询，禁用缓存等于放弃 95% 亚秒承诺的主要手段（DD-36 的快速查询路径依赖缓存）。</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>低（缓存键的构造方式）</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>REQ-SEC-07 · REQ-PRF-01 · DD-35 · DD-41 · DD-36</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>DD-51</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>受控 SQL 只授予自然人，按主体显式授权；系统一律经服务层</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>DD-18 允许授权角色执行只读 SQL，作为不绕过语义层的唯一例外。但用户自行编写的 SQL 无法由服务层拼入过滤条件，若直接访问基表，字段可见性矩阵与部门行过滤将被完全绕过。曾考虑为每个角色预置安全视图并在数据库侧启用行级安全作为纵深防御。</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>改为按主体显式授权，且只授予自然人。RFP 1.6.2.15 的原文是 based on operator role and privileges，按人授予正是 privileges 所指。M-06 中维护一份受控 SQL 授权名单，独立于四角色，字段含主体标识、责任方、授予人、授予时间、到期时间、理由、是否可导出与配额；授权前须校验该主体在 MOI 目录中存在且为自然人账号；撤销即时生效，变更写审计。被授权人可访问其获授范围内的全量数据，该范围内的数据安全由调用方负责——这是组织责任的显式转移，因此授权名单本身须写入我方提交的数据分类政策输入稿，由 MOI 批准，而非本方单方面决定。系统一律经服务层的查询 API、记录检索、对外数据服务与 MCP 绑定访问，那些路径已经过字段矩阵、部门过滤与全程审计，不另开通道。技术护栏与授权无关，一律保留：只读、仅走分析副本、强制超时、结果集上限、SQL 原文与涉及表列的全程审计。结果导出单独配置、单独记审计、可单独关闭。</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>一、为每个角色预置安全视图并在数据库侧启用行级安全。二、把受控 SQL 授予系统管理员角色。三、新增一个业务侧的全量数据角色。四、向系统主体授予受控 SQL（无论是任意 SQL 还是预先登记的语句集）。</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>一、实现与维护成本高，且角色与部门的组合会使视图数量随权限维度增长；按主体授权更贴条款措辞，撤销也更即时。二、系统管理员通常是 IT 人员而非业务人员，让其可自由查询报警人号码、警情描述原文与精确位置，在数据分类政策评审中很可能被挡下；多数合规框架恰恰要求管理员看不到业务敏感数据。三、须 MOI 在目录中增设角色组，与 IR-39 同属周期不可控的外部依赖；按人授权不依赖目录变更。四、系统会持续、高频、无人判断地执行，即便限定为预先登记的语句集，也等于在服务层这个唯一出口旁边另开一扇门；而系统所需的一切访问，服务层的查询 API、记录检索、对外数据服务与 MCP 绑定均已提供，且那些路径自带字段矩阵、部门过滤与审计。开第二条通道没有收益，只有风险（DD-17）。</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>中（授权机制为新增；技术护栏与审计不受影响）</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>REQ-QRY-05 · REQ-SEC-02 · REQ-GOV-02 · REQ-API-02 · DD-17 · DD-18 · DD-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>DD-52</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>新增 mssql_read 连接器，驱动链一律采用开源实现</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>归档库经更正为 SQL Server（CN-36）。连接 SQL Server 需要客户端驱动，而微软官方的 ODBC Driver for SQL Server 是闭源专有软件——若采用，将与 RFP 2.7.3.1「全部软件采用开放许可，使 MOI 具备扩展的灵活性」（REQ-LIC-03）直接冲突，也与 LD-09 中「全部组件为 OSI 认可的开源许可」的表述自相矛盾。</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>新增第五类连接器 mssql_read，驱动链采用 FreeTDS（LGPL）加 unixODBC（LGPL/GPL）加 pyodbc（MIT），或以 pymssql（LGPL，基于 FreeTDS）省去 ODBC 一层。三者均为独立进程或宽松许可的库，符合 LD-09 第 4.2 节的纪律。须在实施前期做一次验证：阿拉伯语字段在 nvarchar 与非 UTF-8 collation 下的读取正确性——FreeTDS 在此历来有坑，不能靠推断。驱动链登记进组件清单，但注明为迁移期组件：对账完成后旧系统下线、IF-01 停用，不需要维护八年；合同期内可能重跑迁移或复核对账，故不删除。</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>一、采用微软官方 ODBC Driver for SQL Server。二、由 DS 或现有运维方把归档数据导出为文件，本方以 file_drop 接入。</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>一、闭源专有软件，与 2.7.3.1 及本方「开源自研、不交付闭源产品」的整体立场冲突（AS-01）。二、看似省事，实则把类型映射与字符集转换的控制权交给了他方——与 DD-04 拒绝「由 DS 定义表结构并写入」是同一条推理：映射的正确性责任仍在我方，控制权却不在；且导出文件会使 raw 层失去源端的原始类型信息，多版本 schema 的反推（DD-37）随之失效。</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>中（连接器为新增；驱动链为迁移期组件，可替换）</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>REQ-MIG-01 · REQ-ING-01 · REQ-LIC-03 · REQ-LIC-06 · CN-36 · DD-04 · DD-37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DD-53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>班次改为派生时间带，不维护排班计划</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>早期设计把「排班计划」列为旁路数据源，由 M-10 人工录入或文件导入，并按其计算 REQ-DSH-04「按班次的坐席绩效」。经与客户核实：排班由各部门 supervisor 自行安排且弹性很大，临时调班不会有人回到 BI 里补录，补录时间也与实际不符。一份长期失准的排班表用来算绩效，比不算更糟——它看起来是权威的。</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>不维护排班计划。班次改为派生属性：core.dim_shift 只登记时间窗口定义（若干行，SCD2，改窗口不改写历史），事件按自身时间戳归入所属窗口，坐席在岗时长由 fact_agent_state 的上岗/下岗区间与窗口求交得出。跨窗口工作的人真实地出现在两个班次中。随之取消：排班的双时间轴、追溯修订后的重算规则、M-10 排班录入的部门行过滤。须在验收前让业务确认口径：报表中的「班次」按时间窗口划分，而非按 supervisor 的排班表划分。</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>一、由 M-10 人工维护排班计划。二、由各部门 supervisor 在 M-10 中各自维护本部门排班，配部门行过滤。</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>一、数据源本身不存在稳定的权威版本，录入即失准；且把绩效口径的正确性押在一项没人有动力维护的手工录入上。二、除继承方案一的全部问题外，还引入一套只为此项存在的录入权限模型，成本与收益不成比例。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>高（时间窗口定义为配置数据；若日后确有权威排班源，可作为新维度接入而不推翻现有口径）</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>REQ-DSH-04 · DD-41 · M-10 · R-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DD-54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>勤务级别保留 CAD 接口为非必选项，不做人工维护</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>勤务级别原记为 M-10 人工维护字段（core.dim_date.duty_level_code），并支撑指标 M-R07。客户答复：勤务级别现未使用。</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>保留 dim_date.duty_level_code 字段与自 CAD 的取数路径，标注为非必选项：源端无值时留空，不阻塞任何作业，不做人工维护。指标 M-R07 版本升为 2、置 depends_unverified 与不发布。客户日后启用时只需在源契约中开启该列，无需改数据模型。</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>一、删除该字段与 M-R07。二、维持 M-10 人工维护。</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>一、字段成本近于零，而删除后再加需要改模型、改分区表、重跑历史；DD-31 已确立「机制预留的代价远小于事后追加」。二、客户不使用的数据不应产生维护动作，人工维护会退化为空表或错表。</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DD-42 · M-R07 · M-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DD-55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>复核与质检不在本系统范围</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HLD 主题域「绩效与质量」列有「复核与质检」，指标 M-P02（质检得分）曾登记为旁路数据源、由人工录入或文件导入。客户明确：RFP 2.3.9.7 的复核与质检属 IRMS。</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>本系统既不采集也不计算质检数据。主题域表述修正为「服务水平、响应时长分布、异常事件」并注明质检归属 IRMS。M-P02 保留在指标册中但清空 source_tables、版本升为 2、标注永不发布，其存在仅用于说明该口径的归属，避免日后有人重新提出而无据可查。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>一、以 file_drop 接入 IRMS 导出的质检结果。</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>一、客户未提出此项集成，RFP 亦未要求；主动扩边界会引入一条无契约、无对账责任方的数据链路，并使本系统对非本系统产生的评分结果承担解释责任。</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>高（若日后客户提出，按标准源接入流程新增契约即可）</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>RFP 2.3.9.7 · M-P02 · AS-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DD-56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>双语译名随源端改名失效待重新确认，不做名称规范化比较</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CAD 多数维度只提供单语名称，另一语种由 M-10 人工维护（REQ-RPT-09）。人工译名描述的是他方系统里的对象：源端一旦改名，旧译名可能只是措辞变化，也可能意味着单位合并、拆分或改隶属，而报表上不会有任何迹象。</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>译名挂在自然键上（译的是实体，不是 SCD2 的某个版本），并记下确认当时源端的原文（meta.label_override.source_label_at_confirm，存原文而非哈希，以便 M-10 待办界面并排显示「确认时是这个、现在是这个」）。源端现值与之不符即置 pending_reconfirm，展现层回落显示源端原文而非可能已失效的旧译名，M-10 列出待办。不做任何名称规范化或格式差异过滤：客户答复改名频率为数年一次，为降误报引入规则表的成本超过其收益，且规则本身在交接时还要解释和维护。M-10 的全部参照数据维护（译名、班次窗口、朝觐期标识）逐字段写 audit.reference_data_change_log——参照数据不经 raw 层，没有 run_log 血缘，此表是唯一追溯来源。</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>一、译名绑定自然键且源端改名不影响（阿英不一致在报表上静默存在）。二、置待确认前先做名称规范化比较，仅在超出纯格式差异时触发。</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>一、最难发现的一类缺陷：报表看起来正常，两列名称指的却可能不是同一个实体。二、为一个数年一遇的误报写规则，属于为不存在的问题增加复杂度；本轮讨论中此方案由本方提出，经客户给出实际频率后自行推翻。</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>REQ-RPT-09 · DD-53 · M-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DD-57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>归档迁移的承诺边界量化为「指标 × 起始可用年份」，并在查询时生效</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>RFP 要求历史数据全量迁移，归档自 2016 年起、中间经历数次系统升级。早期表结构中可能根本不存在某些字段（例如未记录派警时刻），该时段的相关指标算不出来——这不是实现缺陷，是源端信息不存在。风险不在事实本身，而在暴露时点：若在验收演示时客户拉一张 2016 年的响应时长报表发现是空的，即为事故；若在设计阶段写明，它只是一条已知边界。</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>迁移期做一次全量字段可用性剖面：按（字段, 年份）统计行数与非空数，并区分「列在该年结构中不存在」与「列存在但为空」——前者是 schema 版本边界的证据，后者是采集习惯问题（meta.field_availability）。阈值入表不入代码（meta.availability_threshold，初值 available≥95%、partial≥5%、unavailable&lt;5%），因为「多少填充率算可用」是业务口径，客户可能认为 80% 已足以支撑趋势分析。由此逐指标算出起始可用年份，指标继承其全部输入字段中最差的状态，并记下造成该状态的字段名（meta.metric_availability）。该表为机器可读并由服务层在每次查询时读取：查询时段超出可用范围时，报表显示「该时段源端无此数据」并指名限制字段，既不显示空白也不显示零；partial 状态出数但强制显示填充率与样本量、禁用于同比。同一份数据另出静态对照表，随迁移对账报告交付。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>一、仅作为 Word 交付物说明，不入库。二、不区分「列不存在」与「列全空」，一律按空处理。</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>一、文档没人查，报表照样是空白；客户看到的是产品行为，不是附件第 12 页。二、丢掉了推断 schema 版本边界的最强证据（DD-37），且把源端结构变更与业务采集问题混为一谈，后者可能是可补救的、前者不可。</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>中（剖面为一次性作业可重跑；阈值可调；报表提示行为一旦承诺，改动需客户同意）</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>REQ-MIG-01 · REQ-MIG-05 · DD-37 · AS-02 · IR-42</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DD-58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>归档 raw 层不做任何解释，版本判定与结构归一全部置于 staging</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>归档自 2016 年起、经历数次系统升级，且按 AS-02 拿不到升级记录，版本边界只能靠 meta.value_profile 与 meta.field_availability 反推（DD-37 · DD-57）。反推可能推错。问题是推错的代价落在哪一层。</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>原则：raw 层只做「源端原样落地」，不得在装载时应用任何版本判断或列对应关系；版本号、结构归一、字段语义对齐一律由 staging 的 dbt 模型完成。这样推断错了只需 dbt run 重跑，而不必从 SQL Server 重拉十年数据。 raw 的物理表数取决于归档库的实际形态（IR-43，尚未确认）：若为多代表集并存，则每代各落一张 raw.archive_&lt;entity&gt;_v&lt;n&gt;，逐版本登记 source_contract、逐版本对账；若为单库原地升级（表结构只有当前一套、旧行在后加字段上为空），则「原样落地」本就是一张表，版本号是 staging 推断出的标签而非 raw 的分表依据——此时按年代拆分 raw 表反而违背本原则，因为拆分本身就是一次装载期判断。两种形态下不变的是本条原则，变的只是表数。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>一、raw 建一张宽并集表，装载时把各版本字段映射进统一列集，行上带 schema_version_no。二、先在 raw 分年代落表，再在 staging 归一。</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>一、把列对应关系的判断提前到了装载期。判断一旦错，raw 里存的就是错的，只能重拉十年数据。二、在原地升级形态下，「按哪一年属于哪个版本」本身就是待验证的推断，用它决定行落进哪张表，等于把同一个错误提前了一层。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>高（归一逻辑在 dbt，可重跑；raw 表数待 IR-43 答复后确定）</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>REQ-MIG-01 · DD-37 · DD-57 · AS-02 · IR-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DD-59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>语义漂移字段不做映射；归一化范围限定为指标反查出的字段闭包</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>归档十年间系统功能持续增加，早期尤甚。存在一类最难处理的字段：列名未变而含义已变（如优先级由三档改为五档，旧「2」与新「2」不是一回事）。value_profile 能看见取值分布在某时点突变，但看不出新旧档位如何对应——那是业务知识，不在数据里。同时，客户判断早期新增的多数字段业务上并不重要，真正需要动用的概率很小。</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>一、语义漂移默认不映射：保留原始值，加 code_era 标明所属编码体系，报表跨越边界时分段呈现、不做跨期合并；仅当业务方书面给出对照表时才按统一口径映射，并在指标定义中记录该映射的来源与生效区间。理由是三种处理里只有映射会静默改变历史数字，而写进代码后就再也看不见。 二、归一化范围限定为「当前指标口径反查出的字段闭包」，而非全表。闭包外的字段原样保留在 raw、不解释不映射，在 meta.mapping_registry 中状态记为 unknown（而非留空——空白会被遗忘，未知会被统计），note 注明「早期功能字段，当前无指标依赖」。 三、但 meta.field_availability 的剖面覆盖全部列而非仅闭包内：剖面是一次性且低成本的，有了它，将来任何人问「2017 年有没有某字段、填了多少」都能立刻回答，而不必重新扫十年数据。四、随迁移对账报告交付一份「未归一字段清单」，作为将来研究的入口。</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>一、为全部字段建立归一化模型。二、语义漂移字段一律由业务给出对照表后强行映射到统一口径。三、统一降级到最粗的共同粒度（如优先级降为高/非高）以换取全时段可比。</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>一、把成本花在概率很小的用途上；且归一化模型本身要维护八年。二、多数早期字段业务方根本无法给出对照表，等于把迁移卡在一个拿不到的输入上。三、牺牲了近年数据的精度去迁就早期数据，代价方向反了——近年数据才是日常使用的。</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>高（闭包可随指标增加而扩充，届时按同一方法补做归一模型；原始值始终在 raw，未做过不可逆的处理）</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>REQ-MIG-01 · DD-37 · DD-57 · DD-58 · meta.mapping_registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DD-60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>归档时区口径：如实表述源端不含时区的事实，并主动经 Q&amp;A 向 MOI 提出</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>REQ-MIG-08（RFP 2.7.7.5）要求迁移保留原始时区。SQL Server 的 datetime 与 datetime2 不含任何时区信息，只有 datetimeoffset 含。源端实际类型待 IR-42 答复。若源端为无时区类型，则原始时区信息在源端即不存在——任何投标人都迁不出源端没有的东西。风险不在事实，在于何时说、由谁先说。</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>在迁移方案中如实写明分支应对：一、源端为 datetimeoffset 时，映射至 PostgreSQL timestamptz，承诺完整兑现。二、源端为 datetime 或 datetime2 时，保真源端值（映射至 timestamp without time zone），另以元数据声明「该值按 +03 沙特时间解释」，并明确标注此为约定而非源端事实；同时说明原始时区信息在源端即不存在。 并在 Q&amp;A 阶段主动向 MOI 提出该条款与源端实际类型的关系，不等到验收。理由：该事实对全部投标人一致成立，主动提出体现的是复核到了条款级，而非规避条款；反之若不提，验收时被发现则性质完全不同。 无论哪一分支，core 层统一以 timestamptz 存储并显式记录所用时区假设，使下游口径一致（DD-33 同类处理）。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>一、先按可满足表述，待 IR-42 答复后若不满足再补充说明。</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>一、把一个已知的、必然会在验收暴露的问题推到最不利的时点；且若中标后才说明，性质由「投标阶段的技术澄清」变为「交付阶段的减配」。经与客户确认按本条处理（甲案）。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>低（对客表述一经提交即固化；技术实现两分支均已设计，可逆）</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>REQ-MIG-08 · RFP 2.7.7.5 · IR-42 · T-30 · AS-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -1849,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4424,6 +4424,48 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DD-61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DS 增量以水位轮询为基线、逻辑复制为备选，并以滚动窗口校验补偿轮询的固有缺口</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DS CAD 展示库为 PostgreSQL，技术上可做逻辑复制/逻辑解码（CDC）。客户答复中亦有一条「新系统增量接入需具备 CDC 与 API 两种能力」。水位轮询有一个不可回避的固有缺口：源端的物理删除、以及原地更新但未变更时间戳的行，轮询永远看不见——库里那行会一直留着，且不报错。</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>一、基线维持水位轮询（REQ-ING-02）。CDC 唯一不可替代的优势是亚秒延迟与变更捕获，而本系统的延迟要求为分钟级，不需要前者；后者以第二条补偿。 二、无论 CDC 是否谈成，增设滚动窗口校验：近 30 天按日分区比对源端与本方的行数与关键列哈希，差异进待澄清队列。这是不上 CDC 时对物理删除与静默更新唯一现实的补偿，代价为每日一次源端分区级扫描。 三、把逻辑复制作为备选正式列入 IR-02 向 DS 提出，不由本方代为判断对方会拒绝。若 DS 同意，需其提供：wal_level=logical（改此参数要重启展示库）、带 REPLICATION 属性的角色与建槽权限（现仅谈只读 SELECT 账号，见 IR-06）、并维护 PUBLICATION 随 CAD 结构变更。槽的有状态性可用 max_slot_wal_keep_size（PG 13 起）封顶，超限时槽失效而非源端磁盘耗尽，风险由「本方停机可能影响 CAD 展示库」降为「本方需重新全量同步」。若展示库本身为物理备库，逻辑解码需 PG 16 起支持，版本待确认。 四、同批需问清展示库是否存在整表重载式的 ETL 刷新——若有，CDC 会产生海量伪变更，水位轮询同样失效，两种方案都要改。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>一、直接采用逻辑复制作为基线。二、维持纯水位轮询，不加校验也不向 DS 提出 CDC 选项。三、引入 Debezium 一类连接器实现 CDC。</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>一、依赖三项本方无权决定的源端变更，且其中一项要重启他方系统；在这些前提未获书面确认前把它作为基线，等于把交付建在假设上。二、留下一个已知漏洞不作处置；且客户既已提出 CDC 能力，本方不提反而像是回避。将来若出现漏数争议，「提过、对方权衡后选了水位」与「没想到」性质完全不同。三、需引入 JVM 运行时并通常配套 Kafka，在离线环境中意味着新组件、新许可分析与新虚机；而 PostgreSQL 原生逻辑复制订阅可达到同样目的且无此代价。</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>高（水位与 CDC 两条路径的落点同为 raw，切换不影响下游；滚动校验独立于二者，任何情况下都保留）</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>REQ-ING-02 · AS-04 · IR-02 · IR-06 · T-02 · DD-58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
